--- a/Results/TestCases/XLSX/logout_TestCases.xlsx
+++ b/Results/TestCases/XLSX/logout_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -72,7 +72,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_LOGOUT_02</t>
@@ -190,6 +190,9 @@
   </si>
   <si>
     <t>Verify browser forward button does not re-authenticate user after logout</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_LOGOUT_21</t>
@@ -226,7 +229,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -246,12 +249,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFA51D24"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -265,7 +274,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -307,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -316,6 +330,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1401,13 +1418,13 @@
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>19</v>
+      <c r="K21" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1416,13 +1433,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1442,7 +1459,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1451,13 +1468,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1477,7 +1494,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1486,13 +1503,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1512,7 +1529,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1521,13 +1538,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1547,7 +1564,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1556,13 +1573,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>

--- a/Results/TestCases/XLSX/logout_TestCases.xlsx
+++ b/Results/TestCases/XLSX/logout_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="94">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,14 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The OrangeHRM login page is loaded in the browser.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout</t>
+  </si>
+  <si>
+    <t>- The Login button should be visible</t>
   </si>
   <si>
     <t>High</t>
@@ -81,18 +80,34 @@
     <t>Verify dashboard is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/dashboard/index'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_03</t>
   </si>
   <si>
     <t>Verify browser back button does not access dashboard after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate back using the browser's back button</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_04</t>
   </si>
   <si>
     <t>Verify user dropdown is collapsed by default</t>
   </si>
   <si>
+    <t>1. Enter the username and password, then click the Login button</t>
+  </si>
+  <si>
+    <t>- The Logout link should not be visible</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -102,134 +117,220 @@
     <t>Verify user dropdown lists Logout link on click</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user profile dropdown menu</t>
+  </si>
+  <si>
+    <t>- The Logout link should be visible</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_06</t>
   </si>
   <si>
     <t>Verify clicking outside user dropdown closes the dropdown menu</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user profile dropdown menu
+3. Click the page</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_07</t>
   </si>
   <si>
     <t>Verify Logout dropdown item tag is anchor link</t>
   </si>
   <si>
+    <t>- The tag name should equal 'a'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_08</t>
   </si>
   <si>
     <t>Verify cookies are cleared or altered after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">- The length should be greater than '0'
+- The cookies after should be present</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_09</t>
   </si>
   <si>
     <t>Verify Admin page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/admin/viewSystemUsers'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_10</t>
   </si>
   <si>
     <t>Verify PIM page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/pim/viewEmployeeList'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_11</t>
   </si>
   <si>
     <t>Verify Leave page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/leave/viewLeaveList'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_12</t>
   </si>
   <si>
     <t>Verify Time page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/time/viewEmployeeTimesheet'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_13</t>
   </si>
   <si>
     <t>Verify Recruitment page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/recruitment/viewCandidates'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_14</t>
   </si>
   <si>
     <t>Verify My Info page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/pim/viewPersonalDetails/empNumber/7'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_15</t>
   </si>
   <si>
     <t>Verify Buzz page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/buzz/viewBuzz'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_16</t>
   </si>
   <si>
     <t>Verify Directory page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/directory/viewDirectory'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_17</t>
   </si>
   <si>
     <t>Verify Performance page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/performance/searchEvaluatePerformanceReview'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_18</t>
   </si>
   <si>
     <t>Verify Maintenance page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/maintenance/purgeEmployee'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_19</t>
   </si>
   <si>
     <t>Verify Claim page is not accessible after logout</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter the username and password, then click the Login button
+2. Open the user dropdown and click Logout
+3. Navigate directly to '/web/index.php/claim/viewAssignClaim'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_20</t>
   </si>
   <si>
     <t>Verify browser forward button does not re-authenticate user after logout</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
     <t>TC_LOGOUT_21</t>
   </si>
   <si>
     <t>Verify session storage is cleared on logout</t>
   </si>
   <si>
+    <t>- The len should equal '0'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_22</t>
   </si>
   <si>
     <t>Verify localStorage does not contain sensitive tokens after logout</t>
   </si>
   <si>
+    <t>- The token should be null</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_23</t>
   </si>
   <si>
     <t>Verify logout link text matches exact text Logout</t>
   </si>
   <si>
+    <t>- The text should equal 'Logout'</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_24</t>
   </si>
   <si>
     <t>Verify user profile details container elements are not visible after logout</t>
   </si>
   <si>
+    <t>- The top bar should not be visible</t>
+  </si>
+  <si>
     <t>TC_LOGOUT_25</t>
   </si>
   <si>
     <t>Verify logout cursor is a pointer</t>
+  </si>
+  <si>
+    <t>- The cursor should equal 'pointer'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -253,14 +354,8 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFA51D24"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,11 +370,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1E7DD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -321,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -330,9 +420,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -780,7 +867,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>17</v>
@@ -794,7 +881,7 @@
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -803,19 +890,19 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>17</v>
@@ -829,7 +916,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -838,25 +925,25 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -864,7 +951,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -873,25 +960,25 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -899,34 +986,34 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -934,7 +1021,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -943,25 +1030,25 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -969,7 +1056,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -978,13 +1065,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -993,10 +1080,10 @@
         <v>16</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -1004,7 +1091,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1013,25 +1100,25 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1039,7 +1126,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1048,25 +1135,25 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1074,7 +1161,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1083,25 +1170,25 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1109,7 +1196,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1118,25 +1205,25 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1144,7 +1231,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1153,25 +1240,25 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1179,7 +1266,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1188,25 +1275,25 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1214,7 +1301,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1223,25 +1310,25 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1249,7 +1336,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1258,25 +1345,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1284,7 +1371,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1293,25 +1380,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1319,7 +1406,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1328,25 +1415,25 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -1354,7 +1441,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1363,25 +1450,25 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1389,7 +1476,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1398,33 +1485,33 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>59</v>
+        <v>30</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1433,13 +1520,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1448,10 +1535,10 @@
         <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1459,7 +1546,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1468,13 +1555,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1483,10 +1570,10 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1494,7 +1581,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1503,25 +1590,25 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1529,7 +1616,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1538,13 +1625,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1553,10 +1640,10 @@
         <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1564,7 +1651,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1573,25 +1660,25 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>19</v>
